--- a/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/239914_cognizant_com/Documents/2025/Academy work/Digital Nurture/DN 5.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laahiri Indhirani\Desktop\Digital-Nurture-JavaFSE\Deepskilling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{38815D58-CAD9-44C0-B366-FB59C6453CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A83D4995-9CD0-446A-9BFE-55A9EAB2B518}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8656ECD6-848A-4FBD-A6B1-1BD62AB3F36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Java FSE" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -345,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,6 +360,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFBE2D5"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -459,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -475,14 +479,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -495,16 +509,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,30 +862,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57EFDF7-9EDE-4E32-9B50-93240323B319}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.08984375" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" customWidth="1"/>
-    <col min="3" max="3" width="47.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.26953125" customWidth="1"/>
-    <col min="5" max="5" width="30.453125" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="47.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="16"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="10"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -877,133 +899,133 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="20" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="20" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="6" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -1016,7 +1038,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -1029,7 +1051,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1042,7 +1064,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
@@ -1057,7 +1079,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -1072,7 +1094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -1087,7 +1109,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
@@ -1104,7 +1126,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
@@ -1121,7 +1143,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
@@ -1134,7 +1156,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -1147,7 +1169,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>34</v>
       </c>
@@ -1160,7 +1182,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
@@ -1173,7 +1195,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>46</v>
       </c>
@@ -1190,7 +1212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1225,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>46</v>
       </c>
@@ -1216,7 +1238,7 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>46</v>
       </c>
@@ -1229,7 +1251,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>46</v>
       </c>
@@ -1242,7 +1264,7 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>46</v>
       </c>
@@ -1255,33 +1277,33 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="10"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="10"/>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="12"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="12"/>
       <c r="E32" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>63</v>
       </c>
@@ -1298,7 +1320,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>63</v>
       </c>
@@ -1315,7 +1337,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>63</v>
       </c>
@@ -1332,7 +1354,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>63</v>
       </c>
@@ -1345,7 +1367,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>63</v>
       </c>
@@ -1358,7 +1380,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>63</v>
       </c>
@@ -1375,7 +1397,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>63</v>
       </c>
@@ -1392,7 +1414,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>63</v>
       </c>
@@ -1409,7 +1431,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>63</v>
       </c>
@@ -1426,7 +1448,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>63</v>
       </c>
@@ -1443,7 +1465,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>82</v>
       </c>
@@ -1456,7 +1478,7 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>82</v>
       </c>
@@ -1469,7 +1491,7 @@
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>82</v>
       </c>
@@ -1482,7 +1504,7 @@
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>82</v>
       </c>
@@ -1495,7 +1517,7 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>82</v>
       </c>
@@ -1508,18 +1530,18 @@
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="17" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="C48" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1540,6 +1562,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
@@ -1548,15 +1579,6 @@
     <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1820,6 +1842,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -1833,14 +1863,6 @@
     <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laahiri Indhirani\Desktop\Digital-Nurture-JavaFSE\Deepskilling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8656ECD6-848A-4FBD-A6B1-1BD62AB3F36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFA6983-8482-47BE-A775-B905C0625807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
@@ -483,6 +483,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -495,6 +505,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -508,24 +526,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -872,20 +872,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="18"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
+      <c r="A2" s="14"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -900,165 +900,165 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="10" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="4"/>
@@ -1278,16 +1278,16 @@
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="5" t="s">
@@ -1295,10 +1295,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="12"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="16"/>
       <c r="E32" s="6" t="s">
         <v>62</v>
       </c>
@@ -1562,15 +1562,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
@@ -1579,6 +1570,15 @@
     <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1842,14 +1842,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -1863,6 +1855,14 @@
     <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laahiri Indhirani\Desktop\Digital-Nurture-JavaFSE\Deepskilling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFA6983-8482-47BE-A775-B905C0625807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C270EF93-4BE0-49BB-94D6-E4A1C9792AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="122">
   <si>
     <t>Skill</t>
   </si>
@@ -313,6 +313,93 @@
   </si>
   <si>
     <t>Angular Hands-on</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data Structures and Algorithms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 2 </t>
+  </si>
+  <si>
+    <t>Module 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 4 </t>
+  </si>
+  <si>
+    <t>Module 5</t>
+  </si>
+  <si>
+    <t>Module 6</t>
+  </si>
+  <si>
+    <t>Module 7</t>
+  </si>
+  <si>
+    <t>Module 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 9 </t>
+  </si>
+  <si>
+    <t>Module 1</t>
+  </si>
+  <si>
+    <t>PL/SQL Programming</t>
+  </si>
+  <si>
+    <t>Test driven development and Logging framework</t>
+  </si>
+  <si>
+    <t>Code Quality and SonarQube</t>
+  </si>
+  <si>
+    <t>Single Page Application framework - React</t>
+  </si>
+  <si>
+    <t>Application Debugging</t>
+  </si>
+  <si>
+    <t>Version control - GIT</t>
+  </si>
+  <si>
+    <t>DevOps and CICD</t>
+  </si>
+  <si>
+    <t>Containerization using Docker</t>
+  </si>
+  <si>
+    <t>Agile Methodology</t>
+  </si>
+  <si>
+    <t>Cloud Fundamentals</t>
+  </si>
+  <si>
+    <t>Gen AI Fundamentals</t>
+  </si>
+  <si>
+    <t>Module 10</t>
+  </si>
+  <si>
+    <t>Module 11</t>
+  </si>
+  <si>
+    <t>Module 12</t>
+  </si>
+  <si>
+    <t>Module 13</t>
+  </si>
+  <si>
+    <t>Module 14</t>
+  </si>
+  <si>
+    <t>Module 15</t>
+  </si>
+  <si>
+    <t>Module 16</t>
+  </si>
+  <si>
+    <t>Module 17</t>
   </si>
 </sst>
 </file>
@@ -861,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57EFDF7-9EDE-4E32-9B50-93240323B319}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.109375" customWidth="1"/>
@@ -1065,46 +1152,46 @@
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="4" t="s">
         <v>33</v>
       </c>
@@ -1542,6 +1629,142 @@
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>98</v>
+      </c>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>121</v>
+      </c>
+      <c r="B71" t="s">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1562,6 +1785,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
@@ -1570,15 +1802,6 @@
     <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1842,6 +2065,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -1855,14 +2086,6 @@
     <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laahiri Indhirani\Desktop\Digital-Nurture-JavaFSE\Deepskilling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C270EF93-4BE0-49BB-94D6-E4A1C9792AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66682067-D515-4D37-A7F8-CDBBB3992BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="124">
   <si>
     <t>Skill</t>
   </si>
@@ -400,6 +400,12 @@
   </si>
   <si>
     <t>Module 17</t>
+  </si>
+  <si>
+    <t>Module No.</t>
+  </si>
+  <si>
+    <t>Module Name</t>
   </si>
 </sst>
 </file>
@@ -430,7 +436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,6 +459,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -550,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -613,6 +625,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,7 +971,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.109375" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
     <col min="3" max="3" width="47.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.21875" customWidth="1"/>
     <col min="5" max="5" width="30.44140625" customWidth="1"/>
@@ -1630,43 +1649,55 @@
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="14"/>
+      <c r="B54" s="29"/>
+    </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="27" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="27" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="27" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="27" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1767,7 +1798,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A11:A12"/>

--- a/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/Deepskilling/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laahiri Indhirani\Desktop\Digital-Nurture-JavaFSE\Deepskilling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66682067-D515-4D37-A7F8-CDBBB3992BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B80C1DA-7C0D-4543-86C7-9DDC59FC7723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
@@ -436,7 +436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,6 +465,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -562,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -592,10 +598,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -626,13 +639,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,20 +989,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="26"/>
+      <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
+      <c r="A2" s="15"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1110,26 +1121,26 @@
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="20"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
@@ -1216,88 +1227,88 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="30" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="30" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="30" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="30" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="30" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="30" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1384,16 +1395,16 @@
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="18" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="5" t="s">
@@ -1401,10 +1412,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="16"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="16"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="19"/>
       <c r="E32" s="6" t="s">
         <v>62</v>
       </c>
@@ -1650,78 +1661,78 @@
       <c r="E48" s="8"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="16" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
-      <c r="B54" s="29"/>
+      <c r="A54" s="15"/>
+      <c r="B54" s="17"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="13" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="13" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="13" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="32" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="32" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1799,12 +1810,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:C32"/>
@@ -1812,21 +1817,18 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
@@ -1835,6 +1837,15 @@
     <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2098,14 +2109,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -2119,6 +2122,14 @@
     <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
